--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -533,265 +533,18 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>repeated { uint32 type; uint64 value }</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>repeated { uint32 type; uint32 value }</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>repeated { uint32 id; uint32 cost }</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>expr:double expr_params:level</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>enum eSkillType : uint32_t {
- kPassiveSkill = 1 &lt;&lt; 0,    // 被动技能
- kGeneralSkill = 1 &lt;&lt; 1,    // 普通施法技能
- kChannelSkill = 1 &lt;&lt; 2,    // 持续施法技能
- kToggleSkill = 1 &lt;&lt; 3,     // 开关类技能
- kActivateSkill = 1 &lt;&lt; 4,    // 激活类技能
- kBasicAttack   = 1 &lt;&lt; 5  // 普通攻击技能的单独枚举
-};</t>
+          <t>enum eSkillType : uint32_t {</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0技能释放时不需要目标即可释放（如群疗，踩地板技能） -&gt; 1 &lt;&lt; 1
-1技能释放时需要选定目标（单体指向性技能） -&gt; 1 &lt;&lt; 2
-2技能释放时需要以指定地点为目标（常用于AOE技能） -&gt; 1 &lt;&lt; 3</t>
+          <t>0技能释放时不需要目标即可释放（如群疗，踩地板技能） -&gt; 1 &lt;&lt; 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -806,8 +559,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CastPoint(毫秒Spell时间点）,
-一般为动画抬手到攻击帧时长。比如说播放一个挥刀动画0.3秒后动画到攻击点，这时策划就配置CastPoint为0.3秒。</t>
+          <t>CastPoint(毫秒Spell时间点）,</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
